--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484321_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484321_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1695</v>
+        <v>2.9382</v>
       </c>
       <c r="E2" t="n">
-        <v>3.263</v>
+        <v>3.2224</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0935</v>
+        <v>-0.2841</v>
       </c>
       <c r="G2" t="n">
         <v>1.0911</v>
@@ -610,13 +610,13 @@
         <v>1.1721</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5992</v>
+        <v>0.3679</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0221</v>
+        <v>-0.0185</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.3864</v>
       </c>
       <c r="V2" t="n">
         <v>2.2605</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O. TOURE JABBY</t>
+          <t>M. TALAMINO COLLADO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0047</v>
+        <v>1.3023</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9248</v>
+        <v>2.4349</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0799</v>
+        <v>-1.1326</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.2609</v>
+        <v>2.6589</v>
       </c>
       <c r="H3" t="n">
-        <v>1.275</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.5359</v>
+        <v>2.104</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9868</v>
+        <v>3.5526</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4991</v>
+        <v>1.0438</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5122</v>
+        <v>2.5089</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.2478</v>
+        <v>-0.8937</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2241</v>
+        <v>-0.4889</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.0237</v>
+        <v>-0.4049</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.9534</v>
+        <v>-0.586</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1144</v>
+        <v>-0.2277</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4308</v>
+        <v>-0.141</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6836</v>
+        <v>-0.0867</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1046</v>
+        <v>-0.5429</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3327</v>
+        <v>-0.5429</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. TALAMINO COLLADO</t>
+          <t>M. BALLÚS TORRAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0105</v>
+        <v>0.8508</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3338</v>
+        <v>0.7462</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3233</v>
+        <v>0.1045</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6589</v>
+        <v>1.5145</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.7861</v>
       </c>
       <c r="I4" t="n">
-        <v>2.104</v>
+        <v>0.7284</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5526</v>
+        <v>1.9244</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0438</v>
+        <v>0.6562</v>
       </c>
       <c r="L4" t="n">
-        <v>2.5089</v>
+        <v>1.2683</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8937</v>
+        <v>-0.4099</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4889</v>
+        <v>0.13</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4049</v>
+        <v>-0.5399</v>
       </c>
       <c r="P4" t="n">
         <v>-0.586</v>
@@ -766,28 +766,28 @@
         <v>0.3907</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5195</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2421</v>
+        <v>-0.2015</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2774</v>
+        <v>0.1238</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5429</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5429</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. BALLÚS TORRAS</t>
+          <t>O. TOURE JABBY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.2115</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6451</v>
+        <v>0.8125</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0589</v>
+        <v>-0.601</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5145</v>
+        <v>-1.2609</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7861</v>
+        <v>1.275</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7284</v>
+        <v>-2.5359</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9244</v>
+        <v>0.9868</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6562</v>
+        <v>1.4991</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2683</v>
+        <v>-0.5122</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4099</v>
+        <v>-2.2478</v>
       </c>
       <c r="N5" t="n">
-        <v>0.13</v>
+        <v>-0.2241</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5399</v>
+        <v>-2.0237</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.586</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3423</v>
+        <v>1.3213</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3026</v>
+        <v>0.3186</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0397</v>
+        <v>1.0027</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.1046</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.3327</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2756</v>
+        <v>0.1584</v>
       </c>
       <c r="E6" t="n">
-        <v>1.591</v>
+        <v>1.7527</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8666</v>
+        <v>-1.5943</v>
       </c>
       <c r="G6" t="n">
         <v>0.7663</v>
@@ -922,13 +922,13 @@
         <v>0.586</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8419</v>
+        <v>-0.4079</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3494</v>
+        <v>-0.1877</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4925</v>
+        <v>-0.2202</v>
       </c>
       <c r="V6" t="n">
         <v>-0.786</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3304</v>
+        <v>-0.5483</v>
       </c>
       <c r="E7" t="n">
         <v>2.5026</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.833</v>
+        <v>-3.0509</v>
       </c>
       <c r="G7" t="n">
         <v>-1.4281</v>
@@ -1000,13 +1000,13 @@
         <v>1.3674</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5205</v>
+        <v>0.3026</v>
       </c>
       <c r="T7" t="n">
         <v>-0.1594</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.4621</v>
       </c>
       <c r="V7" t="n">
         <v>1.1632</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7454</v>
+        <v>-1.218</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4537</v>
+        <v>-0.1909</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2917</v>
+        <v>-1.0271</v>
       </c>
       <c r="G8" t="n">
         <v>0.3688</v>
@@ -1078,13 +1078,13 @@
         <v>0.7814</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.1045</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4099</v>
+        <v>-0.1471</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9869</v>
+        <v>0.2516</v>
       </c>
       <c r="V8" t="n">
         <v>-1.4959</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0266</v>
+        <v>-1.2348</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8085</v>
+        <v>1.2735</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.8352</v>
+        <v>-2.5084</v>
       </c>
       <c r="G9" t="n">
         <v>1.6727</v>
@@ -1156,13 +1156,13 @@
         <v>0.7814</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8194</v>
+        <v>-0.0275</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5309</v>
+        <v>-0.0659</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2884</v>
+        <v>0.0384</v>
       </c>
       <c r="V9" t="n">
         <v>-0.7312</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1501</v>
+        <v>-1.6755</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.8327</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.7806</v>
+        <v>-2.5082</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1188</v>
@@ -1234,13 +1234,13 @@
         <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7071</v>
+        <v>-0.2325</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4704</v>
+        <v>-0.2682</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2367</v>
+        <v>0.0357</v>
       </c>
       <c r="V10" t="n">
         <v>0.0664</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6677</v>
+        <v>-1.8487</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-0.1504</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0523</v>
+        <v>-1.6983</v>
       </c>
       <c r="G11" t="n">
         <v>-0.281</v>
@@ -1312,13 +1312,13 @@
         <v>0.3907</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.969</v>
+        <v>-0.15</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3961</v>
+        <v>0.0689</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5729</v>
+        <v>-0.2188</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8317</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6123</v>
+        <v>-3.6705</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7021</v>
+        <v>-2.0054</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9103</v>
+        <v>-1.6651</v>
       </c>
       <c r="G12" t="n">
         <v>-2.3347</v>
@@ -1390,13 +1390,13 @@
         <v>0.3907</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4606</v>
+        <v>0.4024</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4458</v>
+        <v>0.1424</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0148</v>
+        <v>0.2599</v>
       </c>
       <c r="V12" t="n">
         <v>-1.1522</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.037199999999999</v>
+        <v>-4.7346</v>
       </c>
       <c r="E13" t="n">
-        <v>10.9281</v>
+        <v>11.2308</v>
       </c>
       <c r="F13" t="n">
         <v>-15.9655</v>
@@ -1435,7 +1435,7 @@
         <v>1.6488</v>
       </c>
       <c r="H13" t="n">
-        <v>2.3229</v>
+        <v>2.322899999999999</v>
       </c>
       <c r="I13" t="n">
         <v>-0.6739999999999995</v>
@@ -1468,13 +1468,13 @@
         <v>7.8138</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0726</v>
+        <v>1.3754</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9620999999999997</v>
+        <v>-0.6594000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>2.0347</v>
+        <v>2.0349</v>
       </c>
       <c r="V13" t="n">
         <v>0.05479999999999996</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.961</v>
+        <v>3.2362</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6539</v>
+        <v>3.1484</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3071</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>-1.4478</v>
@@ -1546,13 +1546,13 @@
         <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0103</v>
+        <v>0.2855</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1377</v>
+        <v>-0.3678</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8726</v>
+        <v>0.6533</v>
       </c>
       <c r="V14" t="n">
         <v>2.8358</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>A. VALLE VIVES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8318</v>
+        <v>2.8869</v>
       </c>
       <c r="E15" t="n">
-        <v>5.2605</v>
+        <v>2.6687</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.4287</v>
+        <v>0.2182</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2096</v>
+        <v>2.3545</v>
       </c>
       <c r="H15" t="n">
-        <v>1.547</v>
+        <v>-0.4106</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3373</v>
+        <v>2.7651</v>
       </c>
       <c r="J15" t="n">
-        <v>2.4434</v>
+        <v>3.2533</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7012</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7422</v>
+        <v>3.1701</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2338</v>
+        <v>-0.8988</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1542</v>
+        <v>-0.4937</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0795</v>
+        <v>-0.4051</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2315</v>
+        <v>-0.6397</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3565</v>
+        <v>-0.5846</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.125</v>
+        <v>-0.0551</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. VALLE VIVES</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4409</v>
+        <v>2.3247</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4665</v>
+        <v>2.7657</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0256</v>
+        <v>-0.4409</v>
       </c>
       <c r="G16" t="n">
-        <v>2.3545</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4106</v>
+        <v>0.1</v>
       </c>
       <c r="I16" t="n">
-        <v>2.7651</v>
+        <v>0.6072</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2533</v>
+        <v>2.5408</v>
       </c>
       <c r="K16" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.0447</v>
       </c>
       <c r="L16" t="n">
-        <v>3.1701</v>
+        <v>2.496</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8988</v>
+        <v>-1.8336</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4937</v>
+        <v>0.0553</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4051</v>
+        <v>-1.8889</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1721</v>
+        <v>1.9534</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0857</v>
+        <v>0.4925</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.0989</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2989</v>
+        <v>0.5915</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.3436</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.1522</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1631</v>
+        <v>2.2187</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9568</v>
+        <v>4.3505</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7936</v>
+        <v>-2.1318</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7072000000000001</v>
+        <v>1.2096</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1</v>
+        <v>1.547</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6072</v>
+        <v>-0.3373</v>
       </c>
       <c r="J17" t="n">
-        <v>2.5408</v>
+        <v>2.4434</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0447</v>
+        <v>1.7012</v>
       </c>
       <c r="L17" t="n">
-        <v>2.496</v>
+        <v>0.7422</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8336</v>
+        <v>-1.2338</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0553</v>
+        <v>-0.1542</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.8889</v>
+        <v>-1.0795</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9534</v>
+        <v>1.3674</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6691</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9078000000000001</v>
+        <v>0.4465</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2388</v>
+        <v>0.1719</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3436</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4959</v>
+        <v>2.4373</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1522</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0171</v>
+        <v>1.5952</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1071</v>
+        <v>0.4996</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1242</v>
+        <v>1.0956</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0496</v>
@@ -1858,13 +1858,13 @@
         <v>1.3674</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3318</v>
+        <v>0.2463</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.1801</v>
       </c>
       <c r="U18" t="n">
-        <v>0.455</v>
+        <v>0.4264</v>
       </c>
       <c r="V18" t="n">
         <v>1.0078</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.698</v>
+        <v>1.2257</v>
       </c>
       <c r="E19" t="n">
-        <v>2.46</v>
+        <v>2.6622</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.762</v>
+        <v>-1.4365</v>
       </c>
       <c r="G19" t="n">
         <v>1.1919</v>
@@ -1936,13 +1936,13 @@
         <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3338</v>
+        <v>-0.8061</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.5846</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.547</v>
+        <v>-0.2215</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3321</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4</v>
+        <v>-0.203</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2857</v>
+        <v>-1.589</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6856</v>
+        <v>1.3861</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4978</v>
@@ -2014,13 +2014,13 @@
         <v>1.3674</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5541</v>
+        <v>-0.0488</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0522</v>
+        <v>-0.3555</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6063</v>
+        <v>0.3067</v>
       </c>
       <c r="V20" t="n">
         <v>0.953</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8546</v>
+        <v>-1.6225</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4754</v>
+        <v>0.2732</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.33</v>
+        <v>-1.8956</v>
       </c>
       <c r="G22" t="n">
         <v>-2.9185</v>
@@ -2170,13 +2170,13 @@
         <v>1.9534</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2356</v>
+        <v>0.4678</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3798</v>
+        <v>0.1776</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1442</v>
+        <v>0.2902</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9298</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4879</v>
+        <v>-2.427</v>
       </c>
       <c r="E23" t="n">
-        <v>1.5037</v>
+        <v>1.4026</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.9916</v>
+        <v>-3.8296</v>
       </c>
       <c r="G23" t="n">
         <v>0.8198</v>
@@ -2248,13 +2248,13 @@
         <v>1.5627</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2845</v>
+        <v>-0.2235</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2337</v>
+        <v>-0.3349</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0507</v>
+        <v>0.1113</v>
       </c>
       <c r="V23" t="n">
         <v>-2.4373</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.8175</v>
+        <v>-2.535</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3179</v>
+        <v>-0.1157</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.4996</v>
+        <v>-2.4193</v>
       </c>
       <c r="G24" t="n">
         <v>-1.7641</v>
@@ -2326,13 +2326,13 @@
         <v>1.7581</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1436</v>
+        <v>0.139</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2337</v>
+        <v>-0.0315</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0902</v>
+        <v>0.1705</v>
       </c>
       <c r="V24" t="n">
         <v>-1.4959</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>5.037299999999999</v>
+        <v>6.385299999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>15.9655</v>
+        <v>15.9656</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.9282</v>
+        <v>-9.5799</v>
       </c>
       <c r="G25" t="n">
         <v>-1.6488</v>
@@ -2374,7 +2374,7 @@
         <v>-2.323</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6741000000000001</v>
+        <v>0.6740999999999997</v>
       </c>
       <c r="J25" t="n">
         <v>14.7339</v>
@@ -2404,13 +2404,13 @@
         <v>15.6274</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0729</v>
+        <v>0.2754999999999999</v>
       </c>
       <c r="T25" t="n">
         <v>-2.0348</v>
       </c>
       <c r="U25" t="n">
-        <v>0.9622999999999999</v>
+        <v>2.3104</v>
       </c>
       <c r="V25" t="n">
         <v>-0.05490000000000061</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484321_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484321_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.3991</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484321_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,11 +715,16 @@
       <c r="X3" t="n">
         <v>-0.5429</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484321_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. BALLÚS TORRAS</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +736,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8508</v>
+        <v>0.607</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7462</v>
+        <v>0.607</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1045</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5145</v>
+        <v>0.607</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7861</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7284</v>
+        <v>0.607</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9244</v>
+        <v>0.607</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6562</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2683</v>
+        <v>0.607</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4099</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5399</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.07770000000000001</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2015</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1238</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -782,12 +797,17 @@
       </c>
       <c r="X4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484321_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. TOURE JABBY</t>
+          <t>A. MARTÍN ADELANTADO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2115</v>
+        <v>0.607</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8125</v>
+        <v>0.607</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.601</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.2609</v>
+        <v>0.607</v>
       </c>
       <c r="H5" t="n">
-        <v>1.275</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.5359</v>
+        <v>0.607</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9868</v>
+        <v>0.607</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4991</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5122</v>
+        <v>0.607</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.2478</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2241</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.0237</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3213</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3186</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0027</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>2.1046</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3327</v>
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484321_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>M. BALLUS TORRAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1584</v>
+        <v>0.5438</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7527</v>
+        <v>0.4392</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5943</v>
+        <v>0.1045</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7663</v>
+        <v>1.2075</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2671</v>
+        <v>0.4792</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4992</v>
+        <v>0.7284</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6046</v>
+        <v>1.6174</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0819</v>
+        <v>0.3492</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5227</v>
+        <v>1.2683</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8382</v>
+        <v>-0.4099</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1852</v>
+        <v>0.13</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.0235</v>
+        <v>-0.5399</v>
       </c>
       <c r="P6" t="n">
-        <v>0.586</v>
+        <v>-0.586</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4079</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1877</v>
+        <v>-0.2015</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2202</v>
+        <v>0.1238</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.786</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1219</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484321_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>M. BALLÚS TORRAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5483</v>
+        <v>0.307</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5026</v>
+        <v>0.307</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.0509</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4281</v>
+        <v>0.307</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.4533</v>
+        <v>0.307</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0253</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9595</v>
+        <v>0.307</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.2244</v>
+        <v>0.307</v>
       </c>
       <c r="L7" t="n">
-        <v>3.184</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.3876</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2289</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.1587</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3026</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1594</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4621</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1632</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.6559</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.4927</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484321_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>O. TOURE JABBY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.218</v>
+        <v>0.2115</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1909</v>
+        <v>0.8125</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0271</v>
+        <v>-0.601</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3688</v>
+        <v>-1.2609</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5981</v>
+        <v>1.275</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2294</v>
+        <v>-2.5359</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9329</v>
+        <v>0.9868</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7572</v>
+        <v>1.4991</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1757</v>
+        <v>-0.5122</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5641</v>
+        <v>-2.2478</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1591</v>
+        <v>-0.2241</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4051</v>
+        <v>-2.0237</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1953</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1045</v>
+        <v>1.3213</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1471</v>
+        <v>0.3186</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2516</v>
+        <v>1.0027</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4959</v>
+        <v>2.1046</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4959</v>
+        <v>-0.3327</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484321_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>M. SALMERON SEGU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2348</v>
+        <v>0.1584</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2735</v>
+        <v>1.7527</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5084</v>
+        <v>-1.5943</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6727</v>
+        <v>0.7663</v>
       </c>
       <c r="H9" t="n">
-        <v>1.6997</v>
+        <v>0.2671</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.027</v>
+        <v>0.4992</v>
       </c>
       <c r="J9" t="n">
-        <v>2.4417</v>
+        <v>2.6046</v>
       </c>
       <c r="K9" t="n">
-        <v>1.659</v>
+        <v>0.0819</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7827</v>
+        <v>2.5227</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.769</v>
+        <v>-1.8382</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0407</v>
+        <v>0.1852</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8097</v>
+        <v>-2.0235</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.1488</v>
+        <v>0.586</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0275</v>
+        <v>-0.4079</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0659</v>
+        <v>-0.1877</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0384</v>
+        <v>-0.2202</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7312</v>
+        <v>-0.786</v>
       </c>
       <c r="W9" t="n">
-        <v>1.8279</v>
+        <v>-0.6642</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.5591</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484321_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>J. JUAREZ GIMENEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6755</v>
+        <v>-0.5483</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8327</v>
+        <v>2.5026</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5082</v>
+        <v>-3.0509</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1188</v>
+        <v>-1.4281</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0663</v>
+        <v>-2.4533</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0525</v>
+        <v>1.0253</v>
       </c>
       <c r="J10" t="n">
-        <v>0.859</v>
+        <v>0.9595</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6971000000000001</v>
+        <v>-2.2244</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1619</v>
+        <v>3.184</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9777</v>
+        <v>-2.3876</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7634</v>
+        <v>-0.2289</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2144</v>
+        <v>-2.1587</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3907</v>
+        <v>-0.586</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2325</v>
+        <v>0.3026</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2682</v>
+        <v>-0.1594</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0357</v>
+        <v>0.4621</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0664</v>
+        <v>1.1632</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2186</v>
+        <v>3.6559</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1522</v>
+        <v>-2.4927</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484321_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8487</v>
+        <v>-1.218</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1504</v>
+        <v>-0.1909</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6983</v>
+        <v>-1.0271</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.281</v>
+        <v>0.3688</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5106000000000001</v>
+        <v>0.5981</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2296</v>
+        <v>-0.2294</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7574</v>
+        <v>0.9329</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1228</v>
+        <v>0.7572</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.1757</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0384</v>
+        <v>-0.5641</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6334</v>
+        <v>-0.1591</v>
       </c>
       <c r="O11" t="n">
         <v>-0.4051</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.586</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.15</v>
+        <v>0.1045</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0689</v>
+        <v>-0.1471</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2188</v>
+        <v>0.2516</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.8317</v>
+        <v>-1.4959</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8317</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484321_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. MARTÍN ADELANTADO</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6705</v>
+        <v>-1.2348</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0054</v>
+        <v>1.2735</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6651</v>
+        <v>-2.5084</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.3347</v>
+        <v>1.6727</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5009</v>
+        <v>1.6997</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.8338</v>
+        <v>-0.027</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.1711</v>
+        <v>2.4417</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1228</v>
+        <v>1.659</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2939</v>
+        <v>0.7827</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1636</v>
+        <v>-0.769</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6237</v>
+        <v>0.0407</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5399</v>
+        <v>-0.8097</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.586</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4024</v>
+        <v>-0.0275</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1424</v>
+        <v>-0.0659</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2599</v>
+        <v>0.0384</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.1522</v>
+        <v>-0.7312</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1522</v>
+        <v>-2.5591</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484321_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. TORNE DELAURENS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,307 +1483,323 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.7346</v>
+        <v>-1.6755</v>
       </c>
       <c r="E13" t="n">
-        <v>11.2308</v>
+        <v>0.8327</v>
       </c>
       <c r="F13" t="n">
-        <v>-15.9655</v>
+        <v>-2.5082</v>
       </c>
       <c r="G13" t="n">
-        <v>1.6488</v>
+        <v>-1.1188</v>
       </c>
       <c r="H13" t="n">
-        <v>2.322899999999999</v>
+        <v>-0.0663</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6739999999999995</v>
+        <v>-1.0525</v>
       </c>
       <c r="J13" t="n">
-        <v>16.3824</v>
+        <v>0.859</v>
       </c>
       <c r="K13" t="n">
-        <v>4.912999999999999</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>11.4698</v>
+        <v>0.1619</v>
       </c>
       <c r="M13" t="n">
-        <v>-14.7335</v>
+        <v>-1.9777</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.5901</v>
+        <v>-0.7634</v>
       </c>
       <c r="O13" t="n">
-        <v>-12.1439</v>
+        <v>-1.2144</v>
       </c>
       <c r="P13" t="n">
-        <v>-7.8136</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q13" t="n">
-        <v>-15.6272</v>
+        <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>7.8138</v>
+        <v>0.586</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3754</v>
+        <v>-0.2325</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6594000000000001</v>
+        <v>-0.2682</v>
       </c>
       <c r="U13" t="n">
-        <v>2.0349</v>
+        <v>0.0357</v>
       </c>
       <c r="V13" t="n">
-        <v>0.05479999999999996</v>
+        <v>0.0664</v>
       </c>
       <c r="W13" t="n">
-        <v>11.1351</v>
+        <v>1.2186</v>
       </c>
       <c r="X13" t="n">
-        <v>-11.0804</v>
+        <v>-1.1522</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484321_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>A. VINALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DM GROUP MOLLET</t>
+          <t>C.B. GRANOLLERS</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2362</v>
+        <v>-2.4557</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1484</v>
+        <v>-0.7574</v>
       </c>
       <c r="F14" t="n">
-        <v>0.08790000000000001</v>
+        <v>-1.6983</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.4478</v>
+        <v>-0.888</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0722</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.3756</v>
+        <v>-0.3774</v>
       </c>
       <c r="J14" t="n">
-        <v>0.665</v>
+        <v>0.1504</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5564</v>
+        <v>0.1228</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1086</v>
+        <v>0.0276</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.1127</v>
+        <v>-1.0384</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.6334</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.4842</v>
+        <v>-0.4051</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5627</v>
+        <v>-0.586</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7581</v>
+        <v>0.3907</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2855</v>
+        <v>-0.15</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3678</v>
+        <v>0.0689</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6533</v>
+        <v>-0.2188</v>
       </c>
       <c r="V14" t="n">
-        <v>2.8358</v>
+        <v>-0.8317</v>
       </c>
       <c r="W14" t="n">
-        <v>3.0466</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2108</v>
+        <v>-0.8317</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484321_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. VALLE VIVES</t>
+          <t>A. MARTIN ADELANTADO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DM GROUP MOLLET</t>
+          <t>C.B. GRANOLLERS</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8869</v>
+        <v>-4.2775</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6687</v>
+        <v>-2.6124</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2182</v>
+        <v>-1.6651</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3545</v>
+        <v>-2.9417</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4106</v>
+        <v>-0.5009</v>
       </c>
       <c r="I15" t="n">
-        <v>2.7651</v>
+        <v>-2.4408</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2533</v>
+        <v>-1.7781</v>
       </c>
       <c r="K15" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.1228</v>
       </c>
       <c r="L15" t="n">
-        <v>3.1701</v>
+        <v>-1.9009</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8988</v>
+        <v>-1.1636</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4937</v>
+        <v>-0.6237</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4051</v>
+        <v>-0.5399</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1721</v>
+        <v>-0.586</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6397</v>
+        <v>0.4024</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5846</v>
+        <v>0.1424</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0551</v>
+        <v>0.2599</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.1522</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.1522</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484321_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DM GROUP MOLLET</t>
+          <t>C.B. GRANOLLERS</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3247</v>
+        <v>-4.7346</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7657</v>
+        <v>11.2308</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4409</v>
+        <v>-15.9655</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7072000000000001</v>
+        <v>1.6488</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1</v>
+        <v>2.323</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6072</v>
+        <v>-0.6739999999999993</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5408</v>
+        <v>16.3824</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0447</v>
+        <v>4.912999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>2.496</v>
+        <v>11.4698</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8336</v>
+        <v>-14.7335</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0553</v>
+        <v>-2.5901</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8889</v>
+        <v>-12.1439</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7814</v>
+        <v>-7.8136</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1721</v>
+        <v>-15.6272</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9534</v>
+        <v>7.813799999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4925</v>
+        <v>1.3754</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0989</v>
+        <v>-0.6594</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5915</v>
+        <v>2.0349</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3436</v>
+        <v>0.05479999999999996</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4959</v>
+        <v>11.1351</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1522</v>
-      </c>
+        <v>-11.0804</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>A. VALLE VIVES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2187</v>
+        <v>2.8869</v>
       </c>
       <c r="E17" t="n">
-        <v>4.3505</v>
+        <v>2.6687</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.1318</v>
+        <v>0.2182</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2096</v>
+        <v>2.3545</v>
       </c>
       <c r="H17" t="n">
-        <v>1.547</v>
+        <v>-0.4106</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3373</v>
+        <v>2.7651</v>
       </c>
       <c r="J17" t="n">
-        <v>2.4434</v>
+        <v>3.2533</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7012</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7422</v>
+        <v>3.1701</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2338</v>
+        <v>-0.8988</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1542</v>
+        <v>-0.4937</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0795</v>
+        <v>-0.4051</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6183999999999999</v>
+        <v>-0.6397</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4465</v>
+        <v>-0.5846</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1719</v>
+        <v>-0.0551</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484321_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5952</v>
+        <v>2.3247</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4996</v>
+        <v>2.7657</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0956</v>
+        <v>-0.4409</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0496</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1445</v>
+        <v>0.1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0949</v>
+        <v>0.6072</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3792</v>
+        <v>2.5408</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2047</v>
+        <v>0.0447</v>
       </c>
       <c r="L18" t="n">
-        <v>1.1745</v>
+        <v>2.496</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4287</v>
+        <v>-1.8336</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3492</v>
+        <v>0.0553</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0795</v>
+        <v>-1.8889</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2463</v>
+        <v>0.4925</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1801</v>
+        <v>-0.0989</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4264</v>
+        <v>0.5915</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0078</v>
+        <v>0.3436</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>1.4959</v>
       </c>
       <c r="X18" t="n">
-        <v>0.7306</v>
+        <v>-1.1522</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484321_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. EXPOSITO FORTUNY</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2257</v>
+        <v>2.2187</v>
       </c>
       <c r="E19" t="n">
-        <v>2.6622</v>
+        <v>4.3505</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4365</v>
+        <v>-2.1318</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1919</v>
+        <v>1.2096</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8547</v>
+        <v>1.547</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3371</v>
+        <v>-0.3373</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3603</v>
+        <v>2.4434</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6181</v>
+        <v>1.7012</v>
       </c>
       <c r="L19" t="n">
         <v>0.7422</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1684</v>
+        <v>-1.2338</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7634</v>
+        <v>-0.1542</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4051</v>
+        <v>-1.0795</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8061</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5846</v>
+        <v>0.4465</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2215</v>
+        <v>0.1719</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8865</v>
+        <v>2.4373</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2186</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484321_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.203</v>
+        <v>2.0222</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.589</v>
+        <v>1.9344</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3861</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.4978</v>
+        <v>-2.6618</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.9693</v>
+        <v>-0.0722</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4716</v>
+        <v>-2.5896</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1433</v>
+        <v>-0.549</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3457</v>
+        <v>0.5564</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2023</v>
+        <v>-1.1054</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3544</v>
+        <v>-2.1127</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6237</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2692</v>
+        <v>-1.4842</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0488</v>
+        <v>0.2855</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3555</v>
+        <v>-0.3678</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3067</v>
+        <v>0.6533</v>
       </c>
       <c r="V20" t="n">
-        <v>0.953</v>
+        <v>2.8358</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8865</v>
+        <v>3.0466</v>
       </c>
       <c r="X20" t="n">
-        <v>0.0664</v>
+        <v>-0.2108</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484321_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>J. AURO GARRIGA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3146</v>
+        <v>1.5952</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1006</v>
+        <v>0.4996</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.214</v>
+        <v>1.0956</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.254</v>
+        <v>-0.0496</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.254</v>
+        <v>-0.1445</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.0949</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0205</v>
+        <v>1.3792</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0205</v>
+        <v>0.2047</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.1745</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2745</v>
+        <v>-1.4287</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2745</v>
+        <v>-0.3492</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-1.0795</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1953</v>
+        <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2559</v>
+        <v>0.2463</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.121</v>
+        <v>-0.1801</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1348</v>
+        <v>0.4264</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.0078</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.7306</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484321_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>G. EXPOSITO FORTUNY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6225</v>
+        <v>1.2257</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2732</v>
+        <v>2.6622</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8956</v>
+        <v>-1.4365</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.9185</v>
+        <v>1.1919</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.446</v>
+        <v>0.8547</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4726</v>
+        <v>0.3371</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5407999999999999</v>
+        <v>2.3603</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.9571</v>
+        <v>1.6181</v>
       </c>
       <c r="L22" t="n">
-        <v>1.4163</v>
+        <v>0.7422</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.3777</v>
+        <v>-1.1684</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4889</v>
+        <v>-0.7634</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.8889</v>
+        <v>-0.4051</v>
       </c>
       <c r="P22" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9534</v>
+        <v>1.1721</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4678</v>
+        <v>-0.8061</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1776</v>
+        <v>-0.5846</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2902</v>
+        <v>-0.2215</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9298</v>
+        <v>-0.3321</v>
       </c>
       <c r="W22" t="n">
-        <v>0.8317</v>
+        <v>0.8865</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.7615</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484321_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>G. VIÑALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.427</v>
+        <v>1.214</v>
       </c>
       <c r="E23" t="n">
-        <v>1.4026</v>
+        <v>1.214</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.8296</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8198</v>
+        <v>1.214</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1046</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7151999999999999</v>
+        <v>1.214</v>
       </c>
       <c r="J23" t="n">
-        <v>2.6676</v>
+        <v>1.214</v>
       </c>
       <c r="K23" t="n">
-        <v>0.738</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1.9295</v>
+        <v>1.214</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.8478</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6334</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2144</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2235</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3349</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1113</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.6559</v>
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484321_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.535</v>
+        <v>-0.203</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1157</v>
+        <v>-1.589</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.4193</v>
+        <v>1.3861</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.7641</v>
+        <v>-1.4978</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3673</v>
+        <v>-1.9693</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.1315</v>
+        <v>0.4716</v>
       </c>
       <c r="J24" t="n">
-        <v>1.0879</v>
+        <v>-1.1433</v>
       </c>
       <c r="K24" t="n">
-        <v>0.926</v>
+        <v>-1.3457</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1619</v>
+        <v>0.2023</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.852</v>
+        <v>-0.3544</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5587</v>
+        <v>-0.6237</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.2933</v>
+        <v>0.2692</v>
       </c>
       <c r="P24" t="n">
-        <v>0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R24" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S24" t="n">
-        <v>0.139</v>
+        <v>-0.0488</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0315</v>
+        <v>-0.3555</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1705</v>
+        <v>0.3067</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.4959</v>
+        <v>0.953</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.4959</v>
+        <v>0.0664</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484321_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,401 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>6.385299999999999</v>
+        <v>-0.3146</v>
       </c>
       <c r="E25" t="n">
+        <v>-0.1006</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.214</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.254</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.254</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.2745</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.2745</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.2559</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.121</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.1348</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484321_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>C. MARZO CHECA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DM GROUP MOLLET</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-1.6225</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.2732</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-1.8956</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-2.9185</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-2.446</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.4726</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.5407999999999999</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-1.9571</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.4163</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-2.3777</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.4889</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-1.8889</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.4678</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.1776</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.2902</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.9298</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.8317</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-1.7615</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484321_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A. REYES QUEZADA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>DM GROUP MOLLET</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-2.427</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.4026</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-3.8296</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.8198</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1046</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.7151999999999999</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.6676</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.9295</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-1.8478</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.6334</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-1.2144</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.2235</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.3349</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.1113</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-3.6559</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484321_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A. SOTO CAPARROS</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>DM GROUP MOLLET</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-2.535</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.1157</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-2.4193</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-1.7641</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-2.1315</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.0879</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-2.852</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-0.5587</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-2.2933</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-0.0315</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.1705</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>play_by_play_2484321_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>DM GROUP MOLLET</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>6.385300000000001</v>
+      </c>
+      <c r="E29" t="n">
         <v>15.9656</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F29" t="n">
         <v>-9.5799</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G29" t="n">
         <v>-1.6488</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H29" t="n">
         <v>-2.323</v>
       </c>
-      <c r="I25" t="n">
-        <v>0.6740999999999997</v>
-      </c>
-      <c r="J25" t="n">
+      <c r="I29" t="n">
+        <v>0.6741000000000001</v>
+      </c>
+      <c r="J29" t="n">
         <v>14.7339</v>
       </c>
-      <c r="K25" t="n">
-        <v>2.5899</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="K29" t="n">
+        <v>2.589900000000001</v>
+      </c>
+      <c r="L29" t="n">
         <v>12.1436</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M29" t="n">
         <v>-16.3824</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N29" t="n">
         <v>-4.9129</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O29" t="n">
         <v>-11.4697</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P29" t="n">
         <v>7.8138</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q29" t="n">
         <v>-7.813700000000001</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R29" t="n">
         <v>15.6274</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S29" t="n">
         <v>0.2754999999999999</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T29" t="n">
         <v>-2.0348</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U29" t="n">
         <v>2.3104</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V29" t="n">
         <v>-0.05490000000000061</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W29" t="n">
         <v>11.0803</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X29" t="n">
         <v>-11.1352</v>
       </c>
+      <c r="Y29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
